--- a/刑事/233/案件資訊/C20250002_233_案件資訊.xlsx
+++ b/刑事/233/案件資訊/C20250002_233_案件資訊.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>起訴</t>
+          <t>二審</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-30</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-06-25 12:20:26</t>
+          <t>2025-06-25 12:31:52</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -698,6 +698,18 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二審</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
